--- a/data/trans_orig/IP09C_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP09C_R-Estudios-trans_orig.xlsx
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3631</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,03%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9733</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,41%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>6796</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6072</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15760</t>
+          <t>16599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -1979,12 +1979,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17268</t>
+          <t>17378</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13869</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24607</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>25488</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>39570</t>
+          <t>38969</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>784</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>14459</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>6984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2177,12 +2177,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,77%</t>
         </is>
       </c>
     </row>
@@ -2205,12 +2205,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2240,12 +2240,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2353,49 +2353,49 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>1872</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
+          <t>8094</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>16,14%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>4638</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>2039</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
           <t>8735</t>
         </is>
       </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>17,42%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>4638</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>9242</t>
-        </is>
-      </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
           <t>5,91%</t>
@@ -2403,12 +2403,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>3894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2746,12 +2746,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>593</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7708</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4782</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11568</t>
+          <t>11465</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2957,12 +2957,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8006</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17786</t>
+          <t>17065</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6962</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3015,12 +3015,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4964</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3085,12 +3085,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7411</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1541</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4875</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12442</t>
+          <t>12558</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3569,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14324</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4109</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12733</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3717,12 +3717,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3732,12 +3732,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3767,12 +3767,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -3795,12 +3795,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>16143</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>27308</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3830,12 +3830,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36292</t>
+          <t>35878</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3865,12 +3865,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>41779</t>
+          <t>43160</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>59183</t>
+          <t>61515</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3923,12 +3923,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7829</t>
+          <t>8390</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18493</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3978,12 +3978,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>14568</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>28048</t>
+          <t>28061</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>16440</t>
+          <t>16447</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>11112</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>23354</t>
+          <t>23252</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9697</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4169,12 +4169,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>3266</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>8385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>578</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4906,12 +4906,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4934,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5963</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4949,12 +4949,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>602</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -5160,12 +5160,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>39,04%</t>
         </is>
       </c>
     </row>
@@ -5273,12 +5273,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2867</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5343,12 +5343,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -5503,12 +5503,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5518,12 +5518,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26963</t>
+          <t>27499</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,18%</t>
         </is>
       </c>
     </row>
@@ -5616,12 +5616,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5631,12 +5631,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11896</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -5842,12 +5842,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23269</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35110</t>
+          <t>34815</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5857,12 +5857,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22527</t>
+          <t>22575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35777</t>
+          <t>35864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>47864</t>
+          <t>49634</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>66578</t>
+          <t>67403</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -5955,12 +5955,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5872</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>8404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11194</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -6068,12 +6068,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>8192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6103,12 +6103,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6138,12 +6138,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15517</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6153,12 +6153,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6216,12 +6216,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6231,12 +6231,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>8352</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20097</t>
+          <t>20080</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6266,12 +6266,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,07%</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6559,12 +6559,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>615</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -6637,12 +6637,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1385</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -6750,12 +6750,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6785,12 +6785,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5785</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>5704</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>6738</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -7089,12 +7089,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>664</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>3879</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>7840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7353</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17334</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7334,12 +7334,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11597</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23192</t>
+          <t>23688</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20746</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>36584</t>
+          <t>36724</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -7432,12 +7432,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2108</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9242</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6155</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15991</t>
+          <t>16481</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -7545,12 +7545,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>10904</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29189</t>
+          <t>29281</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>43768</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7693,12 +7693,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29455</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45289</t>
+          <t>43877</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>62877</t>
+          <t>63055</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>83887</t>
+          <t>84468</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,45%</t>
         </is>
       </c>
     </row>
@@ -7771,12 +7771,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>20688</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -7884,12 +7884,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>12405</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7899,12 +7899,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>16380</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7954,12 +7954,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>11437</t>
+          <t>11622</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>25007</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -7997,12 +7997,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4786</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8012,12 +8012,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17196</t>
+          <t>17633</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13723</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>28019</t>
+          <t>27791</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8463,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,83%</t>
+          <t>47,54%</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,47%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2783</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8867,12 +8867,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>706</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>73,84%</t>
         </is>
       </c>
     </row>
@@ -8915,7 +8915,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>37,17%</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>50,95%</t>
         </is>
       </c>
     </row>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9401,12 +9401,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13282</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9436,12 +9436,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>20785</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>33,4%</t>
         </is>
       </c>
     </row>
@@ -9484,7 +9484,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9519,7 +9519,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9549,12 +9549,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5970</t>
+          <t>5766</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9627,12 +9627,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>582</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -9705,12 +9705,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15684</t>
+          <t>16040</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9775,12 +9775,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>16508</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>29190</t>
+          <t>28864</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -9818,12 +9818,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9888,12 +9888,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4121</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>13526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,74%</t>
         </is>
       </c>
     </row>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8328</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9946,12 +9946,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9966,12 +9966,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9497</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10001,12 +10001,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>15653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -10049,7 +10049,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>4240</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10114,12 +10114,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,66%</t>
         </is>
       </c>
     </row>
@@ -10274,12 +10274,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10309,12 +10309,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10344,12 +10344,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10535,12 +10535,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4851</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10570,12 +10570,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8036</t>
+          <t>8045</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1647</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10628,12 +10628,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3992</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10683,12 +10683,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9034</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>46,34%</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10731,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2680</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10816,7 +10816,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3578</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11027,7 +11027,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -11182,12 +11182,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11197,12 +11197,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11217,12 +11217,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16187</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25435</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -11295,12 +11295,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>515</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11310,12 +11310,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -11408,12 +11408,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1141</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11443,12 +11443,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>1649</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>13037</t>
+          <t>13914</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -11521,12 +11521,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11746</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22045</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11556,12 +11556,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>9280</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>19624</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11591,12 +11591,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23872</t>
+          <t>23926</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>39079</t>
+          <t>37755</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -11634,12 +11634,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2416</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10073</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11649,12 +11649,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11669,12 +11669,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5384</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -11747,12 +11747,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11762,12 +11762,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11721</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11817,12 +11817,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>8099</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6546</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11910,12 +11910,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -11945,12 +11945,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
